--- a/excel-files/MALABON/ACACIA NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/MALABON/ACACIA NATIONAL HIGH SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29823"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8F719F5-5E9D-44B8-B897-D01681C7FF18}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{195654A4-5FAA-4866-9E71-8AAF5F9E09D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22497,12 +22497,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F103:F113 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F91:F101" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L115:L122 L103:L113 L91:L101 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{756E9D48-7A84-4F6B-B100-5A5C39502B07}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
